--- a/jogos_2025-01-29.xlsx
+++ b/jogos_2025-01-29.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Tataouine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,55 +927,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>12.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.68</v>
+        <v>5.05</v>
       </c>
       <c r="N4" t="n">
-        <v>7.25</v>
+        <v>1.22</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X4" t="n">
         <v>3.4</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Y4" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
         <v>2.63</v>
@@ -985,25 +985,25 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '45']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.36</v>
+        <v>7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45686.41666666666</v>
@@ -1030,81 +1030,81 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tataouine</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="O5" t="n">
-        <v>11</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AC5" t="n">
         <v>2.63</v>
@@ -1114,25 +1114,25 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['33', '45']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>4.33</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45686.41666666666</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
         <v>3.94</v>
@@ -1605,47 +1605,47 @@
         <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AB9" t="n">
         <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['3', '20', '54', '74']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" t="n">
         <v>4.5</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
         <v>3.94</v>
@@ -1863,47 +1863,47 @@
         <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AB11" t="n">
         <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['3', '20', '54', '74']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ11" t="n">
         <v>4.5</v>
@@ -2568,32 +2568,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.2</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>1.62</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['4', '85']</t>
+          <t>['35', '45', '45+5']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['17', '38', '90+1']</t>
+          <t>['28', '40']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45686.70833333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>2.79</v>
+        <v>4.52</v>
       </c>
       <c r="N18" t="n">
-        <v>2.61</v>
+        <v>6.47</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['17', '44', '79']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.29</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45686.70833333334</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>4.53</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>7.24</v>
+        <v>4.57</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA19" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['4', '16', '67']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45686.70833333334</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,43 +2991,43 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>3.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.44</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="Y20" t="n">
         <v>1.83</v>
@@ -3036,38 +3036,38 @@
         <v>1.91</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '38', '57', '74', '76', '80']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['16', '80']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.43</v>
+        <v>1.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>6.38</v>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>10.12</v>
       </c>
       <c r="O21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P21" t="n">
         <v>3.1</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q21" t="n">
+        <v>10</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA21" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '62', '77']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.47</v>
+        <v>4.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3213,35 +3213,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>6.38</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>10.12</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['4', '85']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['17', '38', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.73</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['53', '62', '77']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>3.52</v>
       </c>
       <c r="M23" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.38</v>
+        <v>1.81</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
         <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['4', '38', '57', '74', '76', '80']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.33</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>2.56</v>
+        <v>4.53</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>7.24</v>
       </c>
       <c r="O24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>3.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['6', '17', '35', '54']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>3.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="N25" t="n">
-        <v>4.57</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2.2</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['4', '16', '67']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '17', '35', '54']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>2.43</v>
       </c>
       <c r="M26" t="n">
-        <v>4.52</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>6.47</v>
+        <v>2.41</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['17', '44', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6.28</v>
+        <v>2.29</v>
       </c>
       <c r="M27" t="n">
-        <v>4.27</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.36</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.83</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['16', '80']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['5', '13', '45+1', '63']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>4</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45686.70833333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.14</v>
+        <v>6.28</v>
       </c>
       <c r="M28" t="n">
-        <v>6.47</v>
+        <v>4.27</v>
       </c>
       <c r="N28" t="n">
-        <v>10.6</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="P28" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.2</v>
       </c>
-      <c r="S28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X28" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['32', '64']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '13', '45+1', '63']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.75</v>
+        <v>1.07</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.17</v>
+        <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>3</v>
       </c>
       <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.76</v>
+        <v>6.18</v>
       </c>
       <c r="M29" t="n">
-        <v>2.96</v>
+        <v>4.59</v>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>1.35</v>
       </c>
       <c r="O29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.75</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T29" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['45+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['28', '29', '78']</t>
+          <t>['27', '56', '78']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.51</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['3', '5', '60', '90+1']</t>
+          <t>['32', '64']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['36', '38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.45</v>
+        <v>5.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['35', '45', '45+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['28', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4503,35 +4503,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.18</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>4.59</v>
+        <v>2.67</v>
       </c>
       <c r="N32" t="n">
-        <v>1.35</v>
+        <v>3.62</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4602,20 +4602,20 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['27', '56', '78']</t>
+          <t>['74', '83']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.84</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>4.08</v>
+        <v>3.88</v>
       </c>
       <c r="N33" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.48</v>
       </c>
-      <c r="O33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="AC33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['3', '5', '60', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['36', '38']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.14</v>
       </c>
-      <c r="X33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['19', '60']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>2.45</v>
       </c>
-      <c r="AH33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI33" t="n">
-        <v>3</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.36</v>
+        <v>3.25</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="M34" t="n">
-        <v>3.68</v>
+        <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="O34" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['28', '29', '78']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI34" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AJ34" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['38', '42']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45686.70833333334</v>
@@ -4900,16 +4900,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>4.84</v>
       </c>
       <c r="M35" t="n">
-        <v>34</v>
+        <v>4.08</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>1.12</v>
+        <v>5.5</v>
       </c>
       <c r="P35" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="T35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U35" t="n">
         <v>1.62</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.2</v>
       </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['8', '63', '84']</t>
+          <t>['19', '60']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.5</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45686.70833333334</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.6</v>
+        <v>4.69</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>4.03</v>
+        <v>1.56</v>
       </c>
       <c r="O36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['38', '42']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>2.25</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X36" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['47', '72']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['67', '79']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45686.70833333334</v>
@@ -5158,19 +5158,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.52</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>34</v>
       </c>
       <c r="N37" t="n">
-        <v>1.81</v>
+        <v>71</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>1.12</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.63</v>
+        <v>26</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="S37" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>4.33</v>
+        <v>17</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.61</v>
+        <v>3.21</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['8', '63', '84']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.3</v>
+        <v>18.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45686.70833333334</v>
@@ -5277,26 +5277,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.67</v>
+        <v>3.98</v>
       </c>
       <c r="N38" t="n">
-        <v>3.62</v>
+        <v>4.03</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '72']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['74', '83']</t>
+          <t>['67', '79']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45686.70833333334</v>
